--- a/template_files/template_parameters_prepro.xlsx
+++ b/template_files/template_parameters_prepro.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28521"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/u0112736/Documents/MATLAB/net/template_files/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09B4794B-3AE5-D845-A1F1-16455BFC11D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_86E5638F100B77A37C7197D713D25CD5FBB5225B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13060" yWindow="760" windowWidth="17160" windowHeight="18880" xr2:uid="{668F9A64-0E82-7D43-BE0B-34BDD1B9FB4D}"/>
+    <workbookView xWindow="13060" yWindow="760" windowWidth="17160" windowHeight="16220" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="conversion" sheetId="1" r:id="rId1"/>
@@ -18,28 +13,17 @@
     <sheet name="signal_processing" sheetId="3" r:id="rId3"/>
     <sheet name="source_localization" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="199">
   <si>
     <t>parameters_name</t>
   </si>
@@ -53,6 +37,9 @@
     <t>eeg_convert.format</t>
   </si>
   <si>
+    <t>EGI</t>
+  </si>
+  <si>
     <t>EGI, ANT, BP, SPM, EEGLAB</t>
   </si>
   <si>
@@ -77,6 +64,9 @@
     <t>eeg_convert.eeg_channels</t>
   </si>
   <si>
+    <t>1:256</t>
+  </si>
+  <si>
     <t>EEG channels in the data</t>
   </si>
   <si>
@@ -92,6 +82,12 @@
     <t>[Optional] EMG channels used as references for artifact removal</t>
   </si>
   <si>
+    <t>eeg_convert.ecg_channels</t>
+  </si>
+  <si>
+    <t>[Optional] ECG channels used as references for artifact removal</t>
+  </si>
+  <si>
     <t>eeg_convert.kinem_channels</t>
   </si>
   <si>
@@ -122,6 +118,9 @@
     <t>pos_convert.template</t>
   </si>
   <si>
+    <t>egi256_corr</t>
+  </si>
+  <si>
     <t>template electrode positions</t>
   </si>
   <si>
@@ -188,6 +187,9 @@
     <t>leadfield.method</t>
   </si>
   <si>
+    <t>gfdm</t>
+  </si>
+  <si>
     <t>string - Method for head model -  dipoli, simbio, fns, gfdm</t>
   </si>
   <si>
@@ -287,6 +289,27 @@
     <t>bcg_artifacts.ecg_channel</t>
   </si>
   <si>
+    <t>tms_artifacts.enable</t>
+  </si>
+  <si>
+    <t>on or off.  To run EEG-TMS artifact correction</t>
+  </si>
+  <si>
+    <t>tms_options.relative_peak_height</t>
+  </si>
+  <si>
+    <t>X times the median value</t>
+  </si>
+  <si>
+    <t>tms_options.peak_distance</t>
+  </si>
+  <si>
+    <t>in ms</t>
+  </si>
+  <si>
+    <t>tms_options.ntp_artifact</t>
+  </si>
+  <si>
     <t>resampling_bss.enable</t>
   </si>
   <si>
@@ -443,6 +466,39 @@
     <t>muscle_correction.reference_thres</t>
   </si>
   <si>
+    <t>cardiac_correction_options.enable</t>
+  </si>
+  <si>
+    <t>Turn on to detect cardiac artifacts using BSS</t>
+  </si>
+  <si>
+    <t>cardiac_correction_options.bss_method</t>
+  </si>
+  <si>
+    <t>cardiac_correction_options.sampleSize</t>
+  </si>
+  <si>
+    <t>cardiac_correction_options.skewness_enable</t>
+  </si>
+  <si>
+    <t>Turn on to detect cardiiac artifacts using skewness</t>
+  </si>
+  <si>
+    <t>cardiac_correction_options.skewness_thres</t>
+  </si>
+  <si>
+    <t>threshold for skewness. Default value: 1</t>
+  </si>
+  <si>
+    <t>cardiac_correction_options.reference_enable</t>
+  </si>
+  <si>
+    <t>on or off. Turn on to use ECG signal as reference. ECG channels should be defined in "conversion" page</t>
+  </si>
+  <si>
+    <t>cardiac_correction.reference_thres</t>
+  </si>
+  <si>
     <t>despiking.enable</t>
   </si>
   <si>
@@ -564,64 +620,13 @@
   </si>
   <si>
     <t>can be 'trace' or 'lambda1'(svd decomposition)</t>
-  </si>
-  <si>
-    <t>Turn on to detect cardiac artifacts using BSS</t>
-  </si>
-  <si>
-    <t>cardiac_correction_options.enable</t>
-  </si>
-  <si>
-    <t>cardiac_correction_options.bss_method</t>
-  </si>
-  <si>
-    <t>cardiac_correction_options.sampleSize</t>
-  </si>
-  <si>
-    <t>cardiac_correction_options.reference_enable</t>
-  </si>
-  <si>
-    <t>on or off. Turn on to use ECG signal as reference. ECG channels should be defined in "conversion" page</t>
-  </si>
-  <si>
-    <t>cardiac_correction_options.skewness_thres</t>
-  </si>
-  <si>
-    <t>threshold for skewness. Default value: 1</t>
-  </si>
-  <si>
-    <t>cardiac_correction_options.skewness_enable</t>
-  </si>
-  <si>
-    <t>Turn on to detect cardiiac artifacts using skewness</t>
-  </si>
-  <si>
-    <t>cardiac_correction.reference_thres</t>
-  </si>
-  <si>
-    <t>eeg_convert.ecg_channels</t>
-  </si>
-  <si>
-    <t>[Optional] ECG channels used as references for artifact removal</t>
-  </si>
-  <si>
-    <t>EGI</t>
-  </si>
-  <si>
-    <t>egi256_corr</t>
-  </si>
-  <si>
-    <t>gfdm</t>
-  </si>
-  <si>
-    <t>1:256</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -632,11 +637,6 @@
     <font>
       <b/>
       <i/>
-      <sz val="14"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="14"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -1028,16 +1028,13 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1329,13 +1326,44 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1673,17 +1701,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61D98AC3-834B-A142-8F3A-3E9EF081D5FE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="24.95" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="43.1640625" style="11" customWidth="1"/>
-    <col min="2" max="2" width="24.5" style="12" customWidth="1"/>
+    <col min="1" max="1" width="43.125" style="10" customWidth="1"/>
+    <col min="2" max="2" width="24.5" style="11" customWidth="1"/>
     <col min="3" max="3" width="76" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="10.83203125" style="3"/>
+    <col min="4" max="16384" width="10.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="17.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1694,167 +1722,167 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="17.45">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>188</v>
+        <v>4</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="17.45">
       <c r="A3" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="17.45">
       <c r="A4" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" s="6">
         <v>2</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="17.45">
       <c r="A5" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="7">
         <v>5</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="17.45">
       <c r="A6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="108" t="s">
-        <v>191</v>
+        <v>12</v>
+      </c>
+      <c r="B6" s="107" t="s">
+        <v>13</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="17.45">
       <c r="A7" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="8"/>
+        <v>15</v>
+      </c>
+      <c r="B7" s="108"/>
       <c r="C7" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="17.45">
       <c r="A8" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="9"/>
+        <v>17</v>
+      </c>
+      <c r="B8" s="8"/>
       <c r="C8" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="17.45">
       <c r="A9" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="B9" s="9"/>
+        <v>19</v>
+      </c>
+      <c r="B9" s="8"/>
       <c r="C9" s="6" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="17.45">
       <c r="A10" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="9"/>
+        <v>21</v>
+      </c>
+      <c r="B10" s="8"/>
       <c r="C10" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="17.45">
       <c r="A11" s="6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="17.45">
       <c r="A12" s="6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-    </row>
-    <row r="14" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-    </row>
-    <row r="15" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-    </row>
-    <row r="16" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-    </row>
-    <row r="17" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-    </row>
-    <row r="18" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-    </row>
-    <row r="19" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-    </row>
-    <row r="20" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-    </row>
-    <row r="21" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-    </row>
-    <row r="22" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A22" s="10"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-    </row>
-    <row r="23" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A23" s="10"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="17.45">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+    </row>
+    <row r="14" spans="1:3" ht="17.45">
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+    </row>
+    <row r="15" spans="1:3" ht="17.45">
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+    </row>
+    <row r="16" spans="1:3" ht="17.45">
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+    </row>
+    <row r="17" spans="1:3" ht="17.45">
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+    </row>
+    <row r="18" spans="1:3" ht="17.45">
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+    </row>
+    <row r="19" spans="1:3" ht="17.45">
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+    </row>
+    <row r="20" spans="1:3" ht="17.45">
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+    </row>
+    <row r="21" spans="1:3" ht="17.45">
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+    </row>
+    <row r="22" spans="1:3" ht="17.45">
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+    </row>
+    <row r="23" spans="1:3" ht="17.45">
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1862,17 +1890,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2C2074C-4685-FA4E-8B41-772C8A03D7F7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="38.33203125" style="13" customWidth="1"/>
-    <col min="2" max="2" width="32.6640625" style="13" customWidth="1"/>
-    <col min="3" max="3" width="51.83203125" style="13" customWidth="1"/>
-    <col min="4" max="16384" width="10.83203125" style="13"/>
+    <col min="1" max="1" width="38.375" style="12" customWidth="1"/>
+    <col min="2" max="2" width="32.625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="51.875" style="12" customWidth="1"/>
+    <col min="4" max="16384" width="10.875" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="17.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1883,136 +1911,136 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A2" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A3" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="C3" s="19" t="s">
+    <row r="2" spans="1:3" ht="17.45">
+      <c r="A2" s="13" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="20" t="s">
+      <c r="B2" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="C2" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="22" t="s">
+    </row>
+    <row r="3" spans="1:3" ht="17.45">
+      <c r="A3" s="16" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A5" s="23" t="s">
+      <c r="B3" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="C3" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="25" t="s">
+    </row>
+    <row r="4" spans="1:3" ht="17.45">
+      <c r="A4" s="19" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A6" s="23" t="s">
+      <c r="B4" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="C4" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="25" t="s">
+    </row>
+    <row r="5" spans="1:3" ht="17.45">
+      <c r="A5" s="22" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A7" s="23" t="s">
+      <c r="B5" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="C5" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="25" t="s">
+    </row>
+    <row r="6" spans="1:3" ht="17.45">
+      <c r="A6" s="22" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A8" s="23" t="s">
+      <c r="B6" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="C6" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="25" t="s">
+    </row>
+    <row r="7" spans="1:3" ht="17.45">
+      <c r="A7" s="22" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="57" x14ac:dyDescent="0.2">
-      <c r="A9" s="26" t="s">
+      <c r="B7" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="C7" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="25" t="s">
+    </row>
+    <row r="8" spans="1:3" ht="17.45">
+      <c r="A8" s="22" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A10" s="23" t="s">
+      <c r="B8" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="24">
+      <c r="C8" s="24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="52.5">
+      <c r="A9" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="17.45">
+      <c r="A10" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="23">
         <v>1E-4</v>
       </c>
-      <c r="C10" s="25" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="38" x14ac:dyDescent="0.2">
-      <c r="A11" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="B11" s="28" t="s">
-        <v>190</v>
-      </c>
-      <c r="C11" s="29" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A12" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="B12" s="31">
+      <c r="C10" s="24" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="35.1">
+      <c r="A11" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="17.45">
+      <c r="A12" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" s="30">
         <v>2</v>
       </c>
-      <c r="C12" s="32" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A13" s="33" t="s">
-        <v>52</v>
-      </c>
-      <c r="B13" s="33">
+      <c r="C12" s="31" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="17.45">
+      <c r="A13" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" s="32">
         <v>6</v>
       </c>
-      <c r="C13" s="34" t="s">
-        <v>53</v>
+      <c r="C13" s="33" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -2021,617 +2049,677 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2633E451-54E9-204E-B2DD-CC63587DD169}">
-  <dimension ref="A1:C56"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:C60"/>
+  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="49.33203125" customWidth="1"/>
-    <col min="2" max="2" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="49.375" customWidth="1"/>
+    <col min="2" max="2" width="19.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="143" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+    <row r="1" spans="1:3" ht="24.95" customHeight="1">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="34" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="B2" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="38" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="39" t="s">
-        <v>57</v>
-      </c>
-      <c r="B3" s="40" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3" s="41" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="39" t="s">
+    <row r="2" spans="1:3" ht="24.95" customHeight="1">
+      <c r="A2" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="40">
+      <c r="B2" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="37" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="24.95" customHeight="1">
+      <c r="A3" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="40" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="24.95" customHeight="1">
+      <c r="A4" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="39">
         <v>3</v>
       </c>
-      <c r="C4" s="41" t="s">
+      <c r="C4" s="40" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A5" s="41" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" s="42" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="B5" s="43" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="44" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6" s="46">
+      <c r="C5" s="43" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A6" s="44" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="45">
         <v>1</v>
       </c>
-      <c r="C6" s="47" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="45" t="s">
-        <v>66</v>
-      </c>
-      <c r="B7" s="46">
+      <c r="C6" s="46" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A7" s="44" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="45">
         <v>80</v>
       </c>
-      <c r="C7" s="47" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="48" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" s="49" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="50" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="51" t="s">
-        <v>71</v>
-      </c>
-      <c r="B9" s="52" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" s="53" t="s">
+      <c r="C7" s="46" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="51" t="s">
+    <row r="8" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A8" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="B10" s="52">
+      <c r="B8" s="48" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" s="49" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A9" s="50" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="C9" s="52" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A10" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="51">
         <v>5</v>
       </c>
-      <c r="C10" s="53"/>
-    </row>
-    <row r="11" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="51" t="s">
+      <c r="C10" s="52"/>
+    </row>
+    <row r="11" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A11" s="50" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="51">
+        <v>36</v>
+      </c>
+      <c r="C11" s="52"/>
+    </row>
+    <row r="12" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A12" s="50" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="51">
+        <v>80</v>
+      </c>
+      <c r="C12" s="52"/>
+    </row>
+    <row r="13" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A13" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" s="51">
+        <v>10</v>
+      </c>
+      <c r="C13" s="52"/>
+    </row>
+    <row r="14" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A14" s="50" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" s="51">
+        <v>30</v>
+      </c>
+      <c r="C14" s="52"/>
+    </row>
+    <row r="15" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A15" s="50" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" s="51">
+        <v>0</v>
+      </c>
+      <c r="C15" s="52"/>
+    </row>
+    <row r="16" spans="1:3" ht="24.95" customHeight="1">
+      <c r="A16" s="53" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" s="54" t="s">
         <v>75</v>
       </c>
-      <c r="B11" s="52">
-        <v>36</v>
-      </c>
-      <c r="C11" s="53"/>
-    </row>
-    <row r="12" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="51" t="s">
-        <v>76</v>
-      </c>
-      <c r="B12" s="52">
-        <v>80</v>
-      </c>
-      <c r="C12" s="53"/>
-    </row>
-    <row r="13" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="51" t="s">
-        <v>77</v>
-      </c>
-      <c r="B13" s="52">
+      <c r="C16" s="55"/>
+    </row>
+    <row r="17" spans="1:3" ht="24.95" customHeight="1">
+      <c r="A17" s="56" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" s="57">
+        <v>258</v>
+      </c>
+      <c r="C17" s="58"/>
+    </row>
+    <row r="18" spans="1:3" ht="24.95" customHeight="1">
+      <c r="A18" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" s="48" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="49" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="24.95" customHeight="1">
+      <c r="A19" s="56" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" s="57">
         <v>10</v>
       </c>
-      <c r="C13" s="53"/>
-    </row>
-    <row r="14" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="51" t="s">
-        <v>78</v>
-      </c>
-      <c r="B14" s="52">
+      <c r="C19" s="58" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="24.95" customHeight="1">
+      <c r="A20" s="56" t="s">
+        <v>92</v>
+      </c>
+      <c r="B20" s="57">
+        <v>50</v>
+      </c>
+      <c r="C20" s="58" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="24.95" customHeight="1">
+      <c r="A21" s="56" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" s="57">
+        <v>6</v>
+      </c>
+      <c r="C21" s="58" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A22" s="59" t="s">
+        <v>95</v>
+      </c>
+      <c r="B22" s="60" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="61" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A23" s="38" t="s">
+        <v>97</v>
+      </c>
+      <c r="B23" s="39">
+        <v>200</v>
+      </c>
+      <c r="C23" s="40" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A24" s="62" t="s">
+        <v>99</v>
+      </c>
+      <c r="B24" s="63" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="64" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A25" s="65" t="s">
+        <v>101</v>
+      </c>
+      <c r="B25" s="66" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" s="67" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A26" s="65" t="s">
+        <v>104</v>
+      </c>
+      <c r="B26" s="66">
+        <v>1</v>
+      </c>
+      <c r="C26" s="67" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A27" s="62" t="s">
+        <v>106</v>
+      </c>
+      <c r="B27" s="63" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" s="64" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A28" s="65" t="s">
+        <v>108</v>
+      </c>
+      <c r="B28" s="66">
+        <v>5</v>
+      </c>
+      <c r="C28" s="67" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A29" s="65" t="s">
+        <v>110</v>
+      </c>
+      <c r="B29" s="66">
+        <v>12</v>
+      </c>
+      <c r="C29" s="67" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A30" s="62" t="s">
+        <v>112</v>
+      </c>
+      <c r="B30" s="63" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="64" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A31" s="65" t="s">
+        <v>114</v>
+      </c>
+      <c r="B31" s="66">
+        <v>0.2</v>
+      </c>
+      <c r="C31" s="67" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A32" s="68" t="s">
+        <v>116</v>
+      </c>
+      <c r="B32" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="C32" s="70" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A33" s="71" t="s">
+        <v>118</v>
+      </c>
+      <c r="B33" s="72" t="s">
+        <v>119</v>
+      </c>
+      <c r="C33" s="73" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A34" s="71" t="s">
+        <v>121</v>
+      </c>
+      <c r="B34" s="72">
+        <v>1</v>
+      </c>
+      <c r="C34" s="73" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A35" s="71" t="s">
+        <v>123</v>
+      </c>
+      <c r="B35" s="72">
+        <v>7</v>
+      </c>
+      <c r="C35" s="73" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A36" s="68" t="s">
+        <v>125</v>
+      </c>
+      <c r="B36" s="74" t="s">
+        <v>61</v>
+      </c>
+      <c r="C36" s="70" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A37" s="71" t="s">
+        <v>127</v>
+      </c>
+      <c r="B37" s="72">
         <v>30</v>
       </c>
-      <c r="C14" s="53"/>
-    </row>
-    <row r="15" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="B15" s="52">
-        <v>0</v>
-      </c>
-      <c r="C15" s="53"/>
-    </row>
-    <row r="16" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="54" t="s">
-        <v>80</v>
-      </c>
-      <c r="B16" s="55" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="56"/>
-    </row>
-    <row r="17" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="B17" s="58">
-        <v>258</v>
-      </c>
-      <c r="C17" s="59"/>
-    </row>
-    <row r="18" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="60" t="s">
-        <v>82</v>
-      </c>
-      <c r="B18" s="61" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" s="62" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="39" t="s">
-        <v>84</v>
-      </c>
-      <c r="B19" s="40">
+      <c r="C37" s="73" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A38" s="71" t="s">
+        <v>129</v>
+      </c>
+      <c r="B38" s="72">
+        <v>0.8</v>
+      </c>
+      <c r="C38" s="73" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A39" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="B39" s="74" t="s">
+        <v>61</v>
+      </c>
+      <c r="C39" s="70" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A40" s="71" t="s">
+        <v>133</v>
+      </c>
+      <c r="B40" s="72">
+        <v>0.2</v>
+      </c>
+      <c r="C40" s="73" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A41" s="62" t="s">
+        <v>134</v>
+      </c>
+      <c r="B41" s="75" t="s">
+        <v>61</v>
+      </c>
+      <c r="C41" s="64" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="24.95" customHeight="1">
+      <c r="A42" s="65" t="s">
+        <v>136</v>
+      </c>
+      <c r="B42" s="66" t="s">
+        <v>137</v>
+      </c>
+      <c r="C42" s="67" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="24.95" customHeight="1">
+      <c r="A43" s="65" t="s">
+        <v>139</v>
+      </c>
+      <c r="B43" s="66">
+        <v>1</v>
+      </c>
+      <c r="C43" s="67" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A44" s="62" t="s">
+        <v>140</v>
+      </c>
+      <c r="B44" s="75" t="s">
+        <v>61</v>
+      </c>
+      <c r="C44" s="64" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A45" s="65" t="s">
+        <v>142</v>
+      </c>
+      <c r="B45" s="66">
+        <v>0.5</v>
+      </c>
+      <c r="C45" s="67" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A46" s="62" t="s">
+        <v>144</v>
+      </c>
+      <c r="B46" s="75" t="s">
+        <v>61</v>
+      </c>
+      <c r="C46" s="64" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A47" s="65" t="s">
+        <v>146</v>
+      </c>
+      <c r="B47" s="66">
+        <v>0.2</v>
+      </c>
+      <c r="C47" s="67" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A48" s="68" t="s">
+        <v>147</v>
+      </c>
+      <c r="B48" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="C48" s="70" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A49" s="71" t="s">
+        <v>149</v>
+      </c>
+      <c r="B49" s="72" t="s">
+        <v>102</v>
+      </c>
+      <c r="C49" s="73" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A50" s="71" t="s">
+        <v>150</v>
+      </c>
+      <c r="B50" s="72">
+        <v>1</v>
+      </c>
+      <c r="C50" s="73" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A51" s="68" t="s">
+        <v>151</v>
+      </c>
+      <c r="B51" s="74" t="s">
+        <v>61</v>
+      </c>
+      <c r="C51" s="70" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A52" s="71" t="s">
+        <v>153</v>
+      </c>
+      <c r="B52" s="72">
+        <v>1</v>
+      </c>
+      <c r="C52" s="73" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A53" s="68" t="s">
+        <v>155</v>
+      </c>
+      <c r="B53" s="74" t="s">
+        <v>61</v>
+      </c>
+      <c r="C53" s="70" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" s="3" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A54" s="71" t="s">
+        <v>157</v>
+      </c>
+      <c r="B54" s="72">
+        <v>0.2</v>
+      </c>
+      <c r="C54" s="73" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="24.95" customHeight="1">
+      <c r="A55" s="59" t="s">
+        <v>158</v>
+      </c>
+      <c r="B55" s="60" t="s">
+        <v>61</v>
+      </c>
+      <c r="C55" s="61" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="24.95" customHeight="1">
+      <c r="A56" s="38" t="s">
+        <v>160</v>
+      </c>
+      <c r="B56" s="39">
+        <v>0.2</v>
+      </c>
+      <c r="C56" s="40" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="24.95" customHeight="1">
+      <c r="A57" s="41" t="s">
+        <v>162</v>
+      </c>
+      <c r="B57" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="C57" s="43" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="24.95" customHeight="1">
+      <c r="A58" s="44" t="s">
+        <v>164</v>
+      </c>
+      <c r="B58" s="45" t="s">
+        <v>165</v>
+      </c>
+      <c r="C58" s="46" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="24.95" customHeight="1">
+      <c r="A59" s="59" t="s">
+        <v>167</v>
+      </c>
+      <c r="B59" s="60" t="s">
+        <v>75</v>
+      </c>
+      <c r="C59" s="61" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="24.95" customHeight="1">
+      <c r="A60" s="76" t="s">
+        <v>169</v>
+      </c>
+      <c r="B60" s="77">
         <v>200</v>
       </c>
-      <c r="C19" s="41" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="63" t="s">
-        <v>86</v>
-      </c>
-      <c r="B20" s="64" t="s">
-        <v>55</v>
-      </c>
-      <c r="C20" s="65" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="66" t="s">
-        <v>88</v>
-      </c>
-      <c r="B21" s="67" t="s">
-        <v>89</v>
-      </c>
-      <c r="C21" s="68" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="66" t="s">
-        <v>91</v>
-      </c>
-      <c r="B22" s="67">
-        <v>1</v>
-      </c>
-      <c r="C22" s="68" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="63" t="s">
-        <v>93</v>
-      </c>
-      <c r="B23" s="64" t="s">
-        <v>55</v>
-      </c>
-      <c r="C23" s="65" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="66" t="s">
-        <v>95</v>
-      </c>
-      <c r="B24" s="67">
-        <v>5</v>
-      </c>
-      <c r="C24" s="68" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="66" t="s">
-        <v>97</v>
-      </c>
-      <c r="B25" s="67">
-        <v>12</v>
-      </c>
-      <c r="C25" s="68" t="s">
+      <c r="C60" s="78" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="26" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="63" t="s">
-        <v>99</v>
-      </c>
-      <c r="B26" s="64" t="s">
-        <v>55</v>
-      </c>
-      <c r="C26" s="65" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="66" t="s">
-        <v>101</v>
-      </c>
-      <c r="B27" s="67">
-        <v>0.2</v>
-      </c>
-      <c r="C27" s="68" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="69" t="s">
-        <v>103</v>
-      </c>
-      <c r="B28" s="70" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28" s="71" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="72" t="s">
-        <v>105</v>
-      </c>
-      <c r="B29" s="73" t="s">
-        <v>106</v>
-      </c>
-      <c r="C29" s="74" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="72" t="s">
-        <v>108</v>
-      </c>
-      <c r="B30" s="73">
-        <v>1</v>
-      </c>
-      <c r="C30" s="74" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="72" t="s">
-        <v>110</v>
-      </c>
-      <c r="B31" s="73">
-        <v>7</v>
-      </c>
-      <c r="C31" s="74" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="69" t="s">
-        <v>112</v>
-      </c>
-      <c r="B32" s="75" t="s">
-        <v>55</v>
-      </c>
-      <c r="C32" s="71" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="72" t="s">
-        <v>114</v>
-      </c>
-      <c r="B33" s="73">
-        <v>30</v>
-      </c>
-      <c r="C33" s="74" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="72" t="s">
-        <v>116</v>
-      </c>
-      <c r="B34" s="73">
-        <v>0.8</v>
-      </c>
-      <c r="C34" s="74" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="69" t="s">
-        <v>118</v>
-      </c>
-      <c r="B35" s="75" t="s">
-        <v>55</v>
-      </c>
-      <c r="C35" s="71" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="72" t="s">
-        <v>120</v>
-      </c>
-      <c r="B36" s="73">
-        <v>0.2</v>
-      </c>
-      <c r="C36" s="74" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="63" t="s">
-        <v>121</v>
-      </c>
-      <c r="B37" s="76" t="s">
-        <v>55</v>
-      </c>
-      <c r="C37" s="65" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="66" t="s">
-        <v>123</v>
-      </c>
-      <c r="B38" s="67" t="s">
-        <v>124</v>
-      </c>
-      <c r="C38" s="68" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="66" t="s">
-        <v>126</v>
-      </c>
-      <c r="B39" s="67">
-        <v>1</v>
-      </c>
-      <c r="C39" s="68" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="63" t="s">
-        <v>127</v>
-      </c>
-      <c r="B40" s="76" t="s">
-        <v>55</v>
-      </c>
-      <c r="C40" s="65" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="66" t="s">
-        <v>129</v>
-      </c>
-      <c r="B41" s="67">
-        <v>0.5</v>
-      </c>
-      <c r="C41" s="68" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="63" t="s">
-        <v>131</v>
-      </c>
-      <c r="B42" s="76" t="s">
-        <v>55</v>
-      </c>
-      <c r="C42" s="65" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="66" t="s">
-        <v>133</v>
-      </c>
-      <c r="B43" s="67">
-        <v>0.2</v>
-      </c>
-      <c r="C43" s="68" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="69" t="s">
-        <v>176</v>
-      </c>
-      <c r="B44" s="70" t="s">
-        <v>55</v>
-      </c>
-      <c r="C44" s="71" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="72" t="s">
-        <v>177</v>
-      </c>
-      <c r="B45" s="73" t="s">
-        <v>89</v>
-      </c>
-      <c r="C45" s="74" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="72" t="s">
-        <v>178</v>
-      </c>
-      <c r="B46" s="73">
-        <v>1</v>
-      </c>
-      <c r="C46" s="74" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="69" t="s">
-        <v>183</v>
-      </c>
-      <c r="B47" s="75" t="s">
-        <v>55</v>
-      </c>
-      <c r="C47" s="71" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="72" t="s">
-        <v>181</v>
-      </c>
-      <c r="B48" s="73">
-        <v>1</v>
-      </c>
-      <c r="C48" s="74" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="69" t="s">
-        <v>179</v>
-      </c>
-      <c r="B49" s="75" t="s">
-        <v>55</v>
-      </c>
-      <c r="C49" s="71" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" s="3" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="72" t="s">
-        <v>185</v>
-      </c>
-      <c r="B50" s="73">
-        <v>0.2</v>
-      </c>
-      <c r="C50" s="74" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="60" t="s">
-        <v>134</v>
-      </c>
-      <c r="B51" s="61" t="s">
-        <v>55</v>
-      </c>
-      <c r="C51" s="62" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="39" t="s">
-        <v>136</v>
-      </c>
-      <c r="B52" s="40">
-        <v>0.2</v>
-      </c>
-      <c r="C52" s="41" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="42" t="s">
-        <v>138</v>
-      </c>
-      <c r="B53" s="43" t="s">
-        <v>55</v>
-      </c>
-      <c r="C53" s="44" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="45" t="s">
-        <v>140</v>
-      </c>
-      <c r="B54" s="46" t="s">
-        <v>141</v>
-      </c>
-      <c r="C54" s="47" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="60" t="s">
-        <v>143</v>
-      </c>
-      <c r="B55" s="61" t="s">
-        <v>69</v>
-      </c>
-      <c r="C55" s="62" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="77" t="s">
-        <v>145</v>
-      </c>
-      <c r="B56" s="78">
-        <v>200</v>
-      </c>
-      <c r="C56" s="79" t="s">
-        <v>85</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="B1:B1048576">
+  <conditionalFormatting sqref="B1:B17 B22:B1048576">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
+      <formula>"off"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+      <formula>"on"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19:B21">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+      <formula>"off"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
+      <formula>"on"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B18">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"off"</formula>
     </cfRule>
@@ -2640,260 +2728,261 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF21623B-864B-874F-8DEA-99DFC9CCFB34}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="18" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="17.45"/>
   <cols>
-    <col min="1" max="1" width="32.5" style="107" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23" style="107" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="78.6640625" style="107" customWidth="1"/>
-    <col min="4" max="16384" width="10.83203125" style="3"/>
+    <col min="1" max="1" width="32.5" style="106" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23" style="106" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="78.625" style="106" customWidth="1"/>
+    <col min="4" max="16384" width="10.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="80" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="81" t="s">
+      <c r="C1" s="80" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="82" t="s">
-        <v>146</v>
-      </c>
-      <c r="B2" s="83" t="s">
-        <v>147</v>
-      </c>
-      <c r="C2" s="84" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="85" t="s">
-        <v>149</v>
-      </c>
-      <c r="B3" s="86" t="s">
-        <v>147</v>
-      </c>
-      <c r="C3" s="87" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="85" t="s">
-        <v>151</v>
-      </c>
-      <c r="B4" s="88">
+    <row r="2" spans="1:3">
+      <c r="A2" s="81" t="s">
+        <v>170</v>
+      </c>
+      <c r="B2" s="82" t="s">
+        <v>171</v>
+      </c>
+      <c r="C2" s="83" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="84" t="s">
+        <v>173</v>
+      </c>
+      <c r="B3" s="85" t="s">
+        <v>171</v>
+      </c>
+      <c r="C3" s="86" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="84" t="s">
+        <v>175</v>
+      </c>
+      <c r="B4" s="87">
         <v>0.5</v>
       </c>
-      <c r="C4" s="87" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="85" t="s">
-        <v>153</v>
-      </c>
-      <c r="B5" s="88" t="s">
-        <v>147</v>
-      </c>
-      <c r="C5" s="87" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="85" t="s">
-        <v>154</v>
-      </c>
-      <c r="B6" s="86">
+      <c r="C4" s="86" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="84" t="s">
+        <v>177</v>
+      </c>
+      <c r="B5" s="87" t="s">
+        <v>171</v>
+      </c>
+      <c r="C5" s="86" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="84" t="s">
+        <v>178</v>
+      </c>
+      <c r="B6" s="85">
         <v>4</v>
       </c>
-      <c r="C6" s="87"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="85" t="s">
-        <v>155</v>
-      </c>
-      <c r="B7" s="86">
+      <c r="C6" s="86"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="84" t="s">
+        <v>179</v>
+      </c>
+      <c r="B7" s="85">
         <v>8</v>
       </c>
-      <c r="C7" s="87"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="85" t="s">
-        <v>156</v>
-      </c>
-      <c r="B8" s="86" t="s">
-        <v>157</v>
-      </c>
-      <c r="C8" s="87" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="89" t="s">
-        <v>159</v>
-      </c>
-      <c r="B9" s="90">
+      <c r="C7" s="86"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="84" t="s">
+        <v>180</v>
+      </c>
+      <c r="B8" s="85" t="s">
+        <v>181</v>
+      </c>
+      <c r="C8" s="86" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="88" t="s">
+        <v>183</v>
+      </c>
+      <c r="B9" s="89">
         <v>0.05</v>
       </c>
-      <c r="C9" s="91" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="92" t="s">
-        <v>161</v>
-      </c>
-      <c r="B10" s="93">
+      <c r="C9" s="90" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="91" t="s">
+        <v>185</v>
+      </c>
+      <c r="B10" s="92">
         <v>0</v>
       </c>
-      <c r="C10" s="94"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="92" t="s">
-        <v>162</v>
-      </c>
-      <c r="B11" s="93">
+      <c r="C10" s="93"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="91" t="s">
+        <v>186</v>
+      </c>
+      <c r="B11" s="92">
         <v>100</v>
       </c>
-      <c r="C11" s="94"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="95" t="s">
-        <v>163</v>
-      </c>
-      <c r="B12" s="96" t="s">
-        <v>147</v>
-      </c>
-      <c r="C12" s="97"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="95" t="s">
-        <v>164</v>
-      </c>
-      <c r="B13" s="96">
+      <c r="C11" s="93"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="94" t="s">
+        <v>187</v>
+      </c>
+      <c r="B12" s="95" t="s">
+        <v>171</v>
+      </c>
+      <c r="C12" s="96"/>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="94" t="s">
+        <v>188</v>
+      </c>
+      <c r="B13" s="95">
         <v>5</v>
       </c>
-      <c r="C13" s="97"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="95" t="s">
-        <v>165</v>
-      </c>
-      <c r="B14" s="96" t="s">
-        <v>147</v>
-      </c>
-      <c r="C14" s="97"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="95" t="s">
-        <v>166</v>
-      </c>
-      <c r="B15" s="96">
+      <c r="C13" s="96"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="94" t="s">
+        <v>189</v>
+      </c>
+      <c r="B14" s="95" t="s">
+        <v>171</v>
+      </c>
+      <c r="C14" s="96"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="94" t="s">
+        <v>190</v>
+      </c>
+      <c r="B15" s="95">
         <v>0.1</v>
       </c>
-      <c r="C15" s="97"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="95" t="s">
-        <v>167</v>
-      </c>
-      <c r="B16" s="96">
+      <c r="C15" s="96"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="94" t="s">
+        <v>191</v>
+      </c>
+      <c r="B16" s="95">
         <v>0</v>
       </c>
-      <c r="C16" s="97"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="98" t="s">
-        <v>168</v>
-      </c>
-      <c r="B17" s="99">
+      <c r="C16" s="96"/>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="97" t="s">
+        <v>192</v>
+      </c>
+      <c r="B17" s="98">
         <v>10</v>
       </c>
-      <c r="C17" s="100"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="98" t="s">
-        <v>169</v>
-      </c>
-      <c r="B18" s="99">
+      <c r="C17" s="99"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="97" t="s">
+        <v>193</v>
+      </c>
+      <c r="B18" s="98">
         <v>5</v>
       </c>
-      <c r="C18" s="100"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="98" t="s">
-        <v>170</v>
-      </c>
-      <c r="B19" s="99">
+      <c r="C18" s="99"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="97" t="s">
+        <v>194</v>
+      </c>
+      <c r="B19" s="98">
         <v>1</v>
       </c>
-      <c r="C19" s="100"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="101" t="s">
-        <v>171</v>
-      </c>
-      <c r="B20" s="102">
+      <c r="C19" s="99"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="100" t="s">
+        <v>195</v>
+      </c>
+      <c r="B20" s="101">
         <v>0.05</v>
       </c>
-      <c r="C20" s="103"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="104" t="s">
-        <v>172</v>
-      </c>
-      <c r="B21" s="105" t="s">
-        <v>173</v>
-      </c>
-      <c r="C21" s="106" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B22" s="10"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B23" s="10"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B24" s="10"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B25" s="10"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B26" s="10"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B27" s="10"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B28" s="10"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B29" s="10"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B30" s="10"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B31" s="10"/>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B32" s="10"/>
-    </row>
-    <row r="33" spans="2:2" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="10"/>
+      <c r="C20" s="102"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="103" t="s">
+        <v>196</v>
+      </c>
+      <c r="B21" s="104" t="s">
+        <v>197</v>
+      </c>
+      <c r="C21" s="105" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="B22" s="9"/>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="B23" s="9"/>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="B24" s="9"/>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="B25" s="9"/>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="B26" s="9"/>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="B27" s="9"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="B28" s="9"/>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="B29" s="9"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="B30" s="9"/>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="B31" s="9"/>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="B32" s="9"/>
+    </row>
+    <row r="33" spans="2:2" s="3" customFormat="1">
+      <c r="B33" s="9"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
